--- a/gte/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_lattice.xlsx
+++ b/gte/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-25.64178245335264</v>
+        <v>-24.775596722971017</v>
       </c>
       <c r="B1">
-        <v>22.96943711761401</v>
+        <v>23.784071871214312</v>
       </c>
       <c r="C1">
         <v>338.16769933532214</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-22.724681087980837</v>
+        <v>-21.913431331498131</v>
       </c>
       <c r="B2">
-        <v>22.8413450640459</v>
+        <v>23.555264029634753</v>
       </c>
       <c r="C2">
         <v>338.16769933532214</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-20.533529591021697</v>
+        <v>-19.785024323620011</v>
       </c>
       <c r="B3">
-        <v>22.159040477774521</v>
+        <v>22.791034553180939</v>
       </c>
       <c r="C3">
         <v>338.16769933532214</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-18.477894530301732</v>
+        <v>-17.790592632421156</v>
       </c>
       <c r="B4">
-        <v>21.37327846197671</v>
+        <v>21.929043627327697</v>
       </c>
       <c r="C4">
         <v>338.16769933532214</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-16.523939657710763</v>
+        <v>-15.895990487190769</v>
       </c>
       <c r="B5">
-        <v>20.509890652662417</v>
+        <v>20.994207334516844</v>
       </c>
       <c r="C5">
         <v>338.16769933532214</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-14.657329799205296</v>
+        <v>-14.086863760355739</v>
       </c>
       <c r="B6">
-        <v>19.579820964086718</v>
+        <v>19.996999845298532</v>
       </c>
       <c r="C6">
         <v>338.16769933532214</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-12.869579261870102</v>
+        <v>-12.35477278048967</v>
       </c>
       <c r="B7">
-        <v>18.589547636093592</v>
+        <v>18.943579566546138</v>
       </c>
       <c r="C7">
         <v>338.16769933532214</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-11.155396985028265</v>
+        <v>-10.694511110413028</v>
       </c>
       <c r="B8">
-        <v>17.54311002768846</v>
+        <v>17.83774562228859</v>
       </c>
       <c r="C8">
         <v>338.16769933532214</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-9.50707912243535</v>
+        <v>-9.09839301189131</v>
       </c>
       <c r="B9">
-        <v>16.446389492838648</v>
+        <v>16.685106276257834</v>
       </c>
       <c r="C9">
         <v>338.16769933532214</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-7.9164141346825589</v>
+        <v>-7.5582048755885225</v>
       </c>
       <c r="B10">
-        <v>15.30565497414085</v>
+        <v>15.491654978392194</v>
       </c>
       <c r="C10">
         <v>338.16769933532214</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-6.3755724952710811</v>
+        <v>-6.0661009088175746</v>
       </c>
       <c r="B11">
-        <v>14.126883773747142</v>
+        <v>14.263116783752469</v>
       </c>
       <c r="C11">
         <v>338.16769933532214</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.8801565309916448</v>
+        <v>-4.6177137931057715</v>
       </c>
       <c r="B12">
-        <v>12.913433211099768</v>
+        <v>13.002678513571567</v>
       </c>
       <c r="C12">
         <v>338.16769933532214</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.4391139688830878</v>
+        <v>-3.2222222901890234</v>
       </c>
       <c r="B13">
-        <v>11.658472315246181</v>
+        <v>11.703642448648404</v>
       </c>
       <c r="C13">
         <v>338.16769933532214</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.0576582749753052</v>
+        <v>-1.8850020462467869</v>
       </c>
       <c r="B14">
-        <v>10.358020965329134</v>
+        <v>10.362085993575208</v>
       </c>
       <c r="C14">
         <v>338.16769933532214</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.7127204710143239</v>
+        <v>-0.58267016502409119</v>
       </c>
       <c r="B15">
-        <v>9.029690731267296</v>
+        <v>8.995071588551415</v>
       </c>
       <c r="C15">
         <v>338.16769933532214</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>0.61685462583336215</v>
+        <v>0.70621743000199522</v>
       </c>
       <c r="B16">
-        <v>7.6896321324947516</v>
+        <v>7.6182469219264677</v>
       </c>
       <c r="C16">
         <v>338.16769933532214</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1.9162845724355488</v>
+        <v>1.9665909939918851</v>
       </c>
       <c r="B17">
-        <v>6.3265597957311615</v>
+        <v>6.2206156390425509</v>
       </c>
       <c r="C17">
         <v>338.16769933532214</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3.1663717228210171</v>
+        <v>3.178900585597201</v>
       </c>
       <c r="B18">
-        <v>4.9258176455936509</v>
+        <v>4.787912197191778</v>
       </c>
       <c r="C18">
         <v>338.16769933532214</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>4.3661952456282132</v>
+        <v>4.34218929879694</v>
       </c>
       <c r="B19">
-        <v>3.4867026910035177</v>
+        <v>3.3194383444731987</v>
       </c>
       <c r="C19">
         <v>338.16769933532214</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>5.5194035131479886</v>
+        <v>5.4601484864019447</v>
       </c>
       <c r="B20">
-        <v>2.0120002119580964</v>
+        <v>1.8178876516875882</v>
       </c>
       <c r="C20">
         <v>338.16769933532214</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>6.6296448976712083</v>
+        <v>6.5364695012230571</v>
       </c>
       <c r="B21">
-        <v>0.5044954884547278</v>
+        <v>0.28595368963572942</v>
       </c>
       <c r="C21">
         <v>338.16769933532214</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>7.6999049834713</v>
+        <v>7.5741754777690788</v>
       </c>
       <c r="B22">
-        <v>-1.0335321923357062</v>
+        <v>-1.2741575680848896</v>
       </c>
       <c r="C22">
         <v>338.16769933532214</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>8.7305182027519912</v>
+        <v>8.5736166773406453</v>
       </c>
       <c r="B23">
-        <v>-2.6018275145481509</v>
+        <v>-2.8621905366899507</v>
       </c>
       <c r="C23">
         <v>338.16769933532214</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>9.721156199699573</v>
+        <v>9.5344751429363335</v>
       </c>
       <c r="B24">
-        <v>-4.2006411551439928</v>
+        <v>-4.4783772285984069</v>
       </c>
       <c r="C24">
         <v>338.16769933532214</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>10.67149061850035</v>
+        <v>10.45643291755475</v>
       </c>
       <c r="B25">
-        <v>-5.8302237910846406</v>
+        <v>-6.1229496562292383</v>
       </c>
       <c r="C25">
         <v>338.16769933532214</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>11.581058856160325</v>
+        <v>11.339041222254231</v>
       </c>
       <c r="B26">
-        <v>-7.4909285877718315</v>
+        <v>-7.7962352924399836</v>
       </c>
       <c r="C26">
         <v>338.16769933532214</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>12.448861320964371</v>
+        <v>12.181327990332203</v>
       </c>
       <c r="B27">
-        <v>-9.183518664368794</v>
+        <v>-9.4989434518425853</v>
       </c>
       <c r="C27">
         <v>338.16769933532214</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>13.273764174017076</v>
+        <v>12.982190333145843</v>
       </c>
       <c r="B28">
-        <v>-10.908859628479092</v>
+        <v>-11.231878909487566</v>
       </c>
       <c r="C28">
         <v>338.16769933532214</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>14.054633576423015</v>
+        <v>13.74052536205231</v>
       </c>
       <c r="B29">
-        <v>-12.667817087706279</v>
+        <v>-12.995846440425426</v>
       </c>
       <c r="C29">
         <v>338.16769933532214</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>14.790772640724871</v>
+        <v>14.455681309133315</v>
       </c>
       <c r="B30">
-        <v>-14.46092306744157</v>
+        <v>-14.791321638056107</v>
       </c>
       <c r="C30">
         <v>338.16769933532214</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>15.483232285217673</v>
+        <v>15.128810889368573</v>
       </c>
       <c r="B31">
-        <v>-16.287375264226675</v>
+        <v>-16.617463369177173</v>
       </c>
       <c r="C31">
         <v>338.16769933532214</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>16.133500379634558</v>
+        <v>15.761517938462356</v>
       </c>
       <c r="B32">
-        <v>-18.146037792390974</v>
+        <v>-18.473101318935633</v>
       </c>
       <c r="C32">
         <v>338.16769933532214</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>16.743064793708658</v>
+        <v>16.355406292118911</v>
       </c>
       <c r="B33">
-        <v>-20.035774766263835</v>
+        <v>-20.357065172478478</v>
       </c>
       <c r="C33">
         <v>338.16769933532214</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>17.312603493253413</v>
+        <v>16.91126751167992</v>
       </c>
       <c r="B34">
-        <v>-21.956068605820914</v>
+        <v>-22.26877732949864</v>
       </c>
       <c r="C34">
         <v>338.16769933532214</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>17.839554828403518</v>
+        <v>17.426644061036811</v>
       </c>
       <c r="B35">
-        <v>-23.908874953623123</v>
+        <v>-24.210031047872892</v>
       </c>
       <c r="C35">
         <v>338.16769933532214</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>18.320547245373959</v>
+        <v>17.898266129718412</v>
       </c>
       <c r="B36">
-        <v>-25.896767757877672</v>
+        <v>-26.183212300023925</v>
       </c>
       <c r="C36">
         <v>338.16769933532214</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>18.752209190379762</v>
+        <v>18.3228639072536</v>
       </c>
       <c r="B37">
-        <v>-27.922320966791791</v>
+        <v>-28.190707058374493</v>
       </c>
       <c r="C37">
         <v>338.16769933532214</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>19.129241448079629</v>
+        <v>18.695223330760953</v>
       </c>
       <c r="B38">
-        <v>-29.989580164893287</v>
+        <v>-30.236320011408811</v>
       </c>
       <c r="C38">
         <v>338.16769933532214</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>19.438634156907202</v>
+        <v>19.002353327718161</v>
       </c>
       <c r="B39">
-        <v>-32.108477481992452</v>
+        <v>-32.329530711857338</v>
       </c>
       <c r="C39">
         <v>338.16769933532214</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>19.665449793739814</v>
+        <v>19.229318573192629</v>
       </c>
       <c r="B40">
-        <v>-34.290416684220148</v>
+        <v>-34.481237428512053</v>
       </c>
       <c r="C40">
         <v>338.16769933532214</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>19.794750835454813</v>
+        <v>19.361183742251772</v>
       </c>
       <c r="B41">
-        <v>-36.546801537707246</v>
+        <v>-36.702338430164893</v>
       </c>
       <c r="C41">
         <v>338.16769933532214</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>19.794750835454813</v>
+        <v>19.361183742251772</v>
       </c>
       <c r="B42">
-        <v>-36.546801537707246</v>
+        <v>-36.702338430164893</v>
       </c>
       <c r="C42">
         <v>338.16769933532214</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>19.012426091943375</v>
+        <v>18.5656499601249</v>
       </c>
       <c r="B43">
-        <v>-34.788955130792516</v>
+        <v>-34.965514735276955</v>
       </c>
       <c r="C43">
         <v>338.16769933532214</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>18.24473840948146</v>
+        <v>17.7889959370725</v>
       </c>
       <c r="B44">
-        <v>-33.019934339765925</v>
+        <v>-33.214914527989706</v>
       </c>
       <c r="C44">
         <v>338.16769933532214</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>17.478986713915138</v>
+        <v>17.018067865165314</v>
       </c>
       <c r="B45">
-        <v>-31.249435556597767</v>
+        <v>-31.460136108648022</v>
       </c>
       <c r="C45">
         <v>338.16769933532214</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>16.7024699310905</v>
+        <v>16.239711936474098</v>
       </c>
       <c r="B46">
-        <v>-29.487155173258319</v>
+        <v>-29.710777777596764</v>
       </c>
       <c r="C46">
         <v>338.16769933532214</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>15.904298061013362</v>
+        <v>15.442629771345469</v>
       </c>
       <c r="B47">
-        <v>-27.741406951813669</v>
+        <v>-27.9750839338652</v>
       </c>
       <c r="C47">
         <v>338.16769933532214</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>15.080825400328667</v>
+        <v>14.622944703229605</v>
       </c>
       <c r="B48">
-        <v>-26.014974134713235</v>
+        <v>-26.255883371220325</v>
       </c>
       <c r="C48">
         <v>338.16769933532214</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>14.230217319841094</v>
+        <v>13.778635493852532</v>
       </c>
       <c r="B49">
-        <v>-24.309257334502217</v>
+        <v>-24.554650982113515</v>
       </c>
       <c r="C49">
         <v>338.16769933532214</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>13.350639190355347</v>
+        <v>12.907680904940298</v>
       </c>
       <c r="B50">
-        <v>-22.625657163725858</v>
+        <v>-22.872861658996179</v>
       </c>
       <c r="C50">
         <v>338.16769933532214</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>12.440970466445441</v>
+        <v>12.008796254003155</v>
       </c>
       <c r="B51">
-        <v>-20.9650290813429</v>
+        <v>-21.21145283142868</v>
       </c>
       <c r="C51">
         <v>338.16769933532214</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>11.50294693776271</v>
+        <v>11.083643081688187</v>
       </c>
       <c r="B52">
-        <v>-19.326047931966244</v>
+        <v>-19.569212077407336</v>
       </c>
       <c r="C52">
         <v>338.16769933532214</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>10.539018477727817</v>
+        <v>10.134619484426695</v>
       </c>
       <c r="B53">
-        <v>-17.706843406622294</v>
+        <v>-17.944389512037418</v>
       </c>
       <c r="C53">
         <v>338.16769933532214</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>9.5516349597614116</v>
+        <v>9.1641235586499619</v>
       </c>
       <c r="B54">
-        <v>-16.105545196337449</v>
+        <v>-16.33523525042418</v>
       </c>
       <c r="C54">
         <v>338.16769933532214</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>8.5427387603992813</v>
+        <v>8.1740446777793458</v>
       </c>
       <c r="B55">
-        <v>-14.520670430921655</v>
+        <v>-14.740370621565358</v>
       </c>
       <c r="C55">
         <v>338.16769933532214</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>7.51224226863768</v>
+        <v>7.1642373231964234</v>
       </c>
       <c r="B56">
-        <v>-12.952285995318871</v>
+        <v>-13.159901810028389</v>
       </c>
       <c r="C56">
         <v>338.16769933532214</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6.4595503765879956</v>
+        <v>6.1340472532728372</v>
       </c>
       <c r="B57">
-        <v>-11.400846213256589</v>
+        <v>-11.594306214273184</v>
       </c>
       <c r="C57">
         <v>338.16769933532214</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.38406797636161</v>
+        <v>5.0828202263802229</v>
       </c>
       <c r="B58">
-        <v>-9.8668054084622927</v>
+        <v>-10.044061232759631</v>
       </c>
       <c r="C58">
         <v>338.16769933532214</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.2852736477886966</v>
+        <v>4.0099825033869045</v>
       </c>
       <c r="B59">
-        <v>-8.35056164918488</v>
+        <v>-8.5095855214795684</v>
       </c>
       <c r="C59">
         <v>338.16769933532214</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.1629407215746808</v>
+        <v>2.9152823551480438</v>
       </c>
       <c r="B60">
-        <v>-6.852287981758975</v>
+        <v>-6.9910627665527212</v>
       </c>
       <c r="C60">
         <v>338.16769933532214</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.01691621614377</v>
+        <v>1.7985485550154743</v>
       </c>
       <c r="B61">
-        <v>-5.3721011970406005</v>
+        <v>-5.4886179116307439</v>
       </c>
       <c r="C61">
         <v>338.16769933532214</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.84704714992019481</v>
+        <v>0.659609876341053</v>
       </c>
       <c r="B62">
-        <v>-3.9101180858858045</v>
+        <v>-4.0023759003653181</v>
       </c>
       <c r="C62">
         <v>338.16769933532214</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.34621641083870974</v>
+        <v>-0.50108665563912569</v>
       </c>
       <c r="B63">
-        <v>-2.4659950538244688</v>
+        <v>-2.532010539573375</v>
       </c>
       <c r="C63">
         <v>338.16769933532214</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.560012208543111</v>
+        <v>-1.6806210081519459</v>
       </c>
       <c r="B64">
-        <v>-1.0375469650818894</v>
+        <v>-1.0753910887329357</v>
       </c>
       <c r="C64">
         <v>338.16769933532214</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.790874937770051</v>
+        <v>-2.8754548965400377</v>
       </c>
       <c r="B65">
-        <v>0.37787170144278764</v>
+        <v>0.37006432951270946</v>
       </c>
       <c r="C65">
         <v>338.16769933532214</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.0353392930965768</v>
+        <v>-4.0820500361460352</v>
       </c>
       <c r="B66">
-        <v>1.7829064668504164</v>
+        <v>1.8069375925202726</v>
       </c>
       <c r="C66">
         <v>338.16769933532214</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-5.2945589554386165</v>
+        <v>-5.3015578497618145</v>
       </c>
       <c r="B67">
-        <v>3.1766765755266331</v>
+        <v>3.23438850999354</v>
       </c>
       <c r="C67">
         <v>338.16769933532214</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-6.5881635510676384</v>
+        <v>-6.5538885899762471</v>
       </c>
       <c r="B68">
-        <v>4.5441961649962241</v>
+        <v>4.63788862102462</v>
       </c>
       <c r="C68">
         <v>338.16769933532214</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-7.9314419592628038</v>
+        <v>-7.8545340256941305</v>
       </c>
       <c r="B69">
-        <v>5.8737932329954257</v>
+        <v>6.0061336210637517</v>
       </c>
       <c r="C69">
         <v>338.16769933532214</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-9.3038441259784452</v>
+        <v>-9.1825531612869291</v>
       </c>
       <c r="B70">
-        <v>7.1811563249670938</v>
+        <v>7.3544041016053514</v>
       </c>
       <c r="C70">
         <v>338.16769933532214</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-10.682968629267823</v>
+        <v>-10.515117281771271</v>
       </c>
       <c r="B71">
-        <v>8.4833873777438864</v>
+        <v>8.699358118178008</v>
       </c>
       <c r="C71">
         <v>338.16769933532214</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-12.074847508904645</v>
+        <v>-11.858279559277648</v>
       </c>
       <c r="B72">
-        <v>9.7758813460109426</v>
+        <v>10.036578686402734</v>
       </c>
       <c r="C72">
         <v>338.16769933532214</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-13.489324522846941</v>
+        <v>-13.22195903625558</v>
       </c>
       <c r="B73">
-        <v>11.051123201160056</v>
+        <v>11.35882790611586</v>
       </c>
       <c r="C73">
         <v>338.16769933532214</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-14.923056840069586</v>
+        <v>-14.60265634931682</v>
       </c>
       <c r="B74">
-        <v>12.31166496355717</v>
+        <v>12.668659253922559</v>
       </c>
       <c r="C74">
         <v>338.16769933532214</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-16.369355088141734</v>
+        <v>-15.993461720271926</v>
       </c>
       <c r="B75">
-        <v>13.562613506553191</v>
+        <v>13.971114777474387</v>
       </c>
       <c r="C75">
         <v>338.16769933532214</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-17.821330317992828</v>
+        <v>-17.387242117564419</v>
       </c>
       <c r="B76">
-        <v>14.809228066464813</v>
+        <v>15.271399431839603</v>
       </c>
       <c r="C76">
         <v>338.16769933532214</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-19.272703452992516</v>
+        <v>-18.777472421529751</v>
       </c>
       <c r="B77">
-        <v>16.056302284166939</v>
+        <v>16.574274580317987</v>
       </c>
       <c r="C77">
         <v>338.16769933532214</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-20.719834482910912</v>
+        <v>-20.160282413438</v>
       </c>
       <c r="B78">
-        <v>17.306615055801494</v>
+        <v>17.882564311718639</v>
       </c>
       <c r="C78">
         <v>338.16769933532214</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-22.155998079200582</v>
+        <v>-21.52865278904639</v>
       </c>
       <c r="B79">
-        <v>18.565300704728408</v>
+        <v>19.201390594576932</v>
       </c>
       <c r="C79">
         <v>338.16769933532214</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-23.568857762443084</v>
+        <v>-22.869831248990348</v>
       </c>
       <c r="B80">
-        <v>19.841777280045342</v>
+        <v>20.54005874945458</v>
       </c>
       <c r="C80">
         <v>338.16769933532214</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-24.926781918227725</v>
+        <v>-24.151428512649161</v>
       </c>
       <c r="B81">
-        <v>21.160193332360024</v>
+        <v>21.922203152421506</v>
       </c>
       <c r="C81">
         <v>338.16769933532214</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-25.64178245335264</v>
+        <v>-24.775596722971017</v>
       </c>
       <c r="B82">
-        <v>22.96943711761401</v>
+        <v>23.784071871214312</v>
       </c>
       <c r="C82">
         <v>338.16769933532214</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-35.7113022060782</v>
+        <v>-35.492043909343245</v>
       </c>
       <c r="B1">
-        <v>16.589349043142207</v>
+        <v>17.026847403609086</v>
       </c>
       <c r="C1">
         <v>410.1621514722421</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-33.345173590522045</v>
+        <v>-33.139743437865484</v>
       </c>
       <c r="B2">
-        <v>16.391099861354178</v>
+        <v>16.788703868449439</v>
       </c>
       <c r="C2">
         <v>410.1621514722421</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-31.177068117801937</v>
+        <v>-30.987517231708679</v>
       </c>
       <c r="B3">
-        <v>15.826602764591899</v>
+        <v>16.186995901614495</v>
       </c>
       <c r="C3">
         <v>410.1621514722421</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-29.043055515165403</v>
+        <v>-28.869193974063595</v>
       </c>
       <c r="B4">
-        <v>15.199050196611614</v>
+        <v>15.52368127993063</v>
       </c>
       <c r="C4">
         <v>410.1621514722421</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-26.934008983651616</v>
+        <v>-26.775526660590479</v>
       </c>
       <c r="B5">
-        <v>14.525322361625406</v>
+        <v>14.815563173321202</v>
       </c>
       <c r="C5">
         <v>410.1621514722421</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-24.846199142989953</v>
+        <v>-24.702739371232681</v>
       </c>
       <c r="B6">
-        <v>13.812316825890955</v>
+        <v>14.069502985111853</v>
       </c>
       <c r="C6">
         <v>410.1621514722421</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-22.777492231432458</v>
+        <v>-22.64867329708056</v>
       </c>
       <c r="B7">
-        <v>13.063980026072402</v>
+        <v>13.28942358930675</v>
       </c>
       <c r="C7">
         <v>410.1621514722421</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-20.726628744972544</v>
+        <v>-20.612055682139104</v>
       </c>
       <c r="B8">
-        <v>12.282641440985756</v>
+        <v>12.477637771157129</v>
       </c>
       <c r="C8">
         <v>410.1621514722421</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-18.691648206030521</v>
+        <v>-18.590902788920218</v>
       </c>
       <c r="B9">
-        <v>11.471927014627413</v>
+        <v>11.637750274088115</v>
       </c>
       <c r="C9">
         <v>410.1621514722421</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-16.670435517420433</v>
+        <v>-16.583073946827422</v>
       </c>
       <c r="B10">
-        <v>10.635748663166529</v>
+        <v>10.773651012115208</v>
       </c>
       <c r="C10">
         <v>410.1621514722421</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-14.66095807710429</v>
+        <v>-14.586511734323784</v>
       </c>
       <c r="B11">
-        <v>9.7778657262829114</v>
+        <v>9.8890786234415344</v>
       </c>
       <c r="C11">
         <v>410.1621514722421</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-12.662126888210461</v>
+        <v>-12.600115079645729</v>
       </c>
       <c r="B12">
-        <v>8.9002923263055731</v>
+        <v>8.9860339177630131</v>
       </c>
       <c r="C12">
         <v>410.1621514722421</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-10.676544879384778</v>
+        <v>-10.626525061063592</v>
       </c>
       <c r="B13">
-        <v>7.9982142926496733</v>
+        <v>8.05971766655906</v>
       </c>
       <c r="C13">
         <v>410.1621514722421</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-8.7057662053869223</v>
+        <v>-8.6673194251473937</v>
       </c>
       <c r="B14">
-        <v>7.068757183812413</v>
+        <v>7.1072628717470572</v>
       </c>
       <c r="C14">
         <v>410.1621514722421</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-6.743457999914571</v>
+        <v>-6.7160804416319841</v>
       </c>
       <c r="B15">
-        <v>6.1236337675330441</v>
+        <v>6.1403314952127461</v>
       </c>
       <c r="C15">
         <v>410.1621514722421</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-4.7838117989706017</v>
+        <v>-4.766921806093813</v>
       </c>
       <c r="B16">
-        <v>5.1735869185972341</v>
+        <v>5.1696198197538514</v>
       </c>
       <c r="C16">
         <v>410.1621514722421</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.8310037688406564</v>
+        <v>-2.824078394310801</v>
       </c>
       <c r="B17">
-        <v>4.2108927307342308</v>
+        <v>4.1874324518476307</v>
       </c>
       <c r="C17">
         <v>410.1621514722421</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.8904288701279105</v>
+        <v>-0.89302036587705824</v>
       </c>
       <c r="B18">
-        <v>3.2255731122726066</v>
+        <v>3.1838293051925457</v>
       </c>
       <c r="C18">
         <v>410.1621514722421</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.03762738957711</v>
+        <v>1.0259621645500221</v>
       </c>
       <c r="B19">
-        <v>2.2171000109946557</v>
+        <v>2.1582831986923252</v>
       </c>
       <c r="C19">
         <v>410.1621514722421</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.95415686593708</v>
+        <v>2.9338740935472685</v>
       </c>
       <c r="B20">
-        <v>1.1873078845460825</v>
+        <v>1.1126201775519953</v>
       </c>
       <c r="C20">
         <v>410.1621514722421</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.8601514146146521</v>
+        <v>4.8317203176914836</v>
       </c>
       <c r="B21">
-        <v>0.13803119057260396</v>
+        <v>0.048666286976593254</v>
       </c>
       <c r="C21">
         <v>410.1621514722421</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.7564260380030925</v>
+        <v>6.7203266367613477</v>
       </c>
       <c r="B22">
-        <v>-0.92922270707447319</v>
+        <v>-1.0320778731104865</v>
       </c>
       <c r="C22">
         <v>410.1621514722421</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>8.6430883254181143</v>
+        <v>8.5998024633430319</v>
       </c>
       <c r="B23">
-        <v>-2.0142548197214714</v>
+        <v>-2.1294134839124212</v>
       </c>
       <c r="C23">
         <v>410.1621514722421</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>10.520069012906024</v>
+        <v>10.470078113224563</v>
       </c>
       <c r="B24">
-        <v>-3.1171932524891122</v>
+        <v>-3.2434671719140185</v>
       </c>
       <c r="C24">
         <v>410.1621514722421</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>12.387298836513137</v>
+        <v>12.331083902193981</v>
       </c>
       <c r="B25">
-        <v>-4.238166110498125</v>
+        <v>-4.3743655636000938</v>
       </c>
       <c r="C25">
         <v>410.1621514722421</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>14.244678849957371</v>
+        <v>14.182720231341291</v>
       </c>
       <c r="B26">
-        <v>-5.377356396952008</v>
+        <v>-5.5222896448712895</v>
       </c>
       <c r="C26">
         <v>410.1621514722421</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>16.091991377643069</v>
+        <v>16.024767842964426</v>
       </c>
       <c r="B27">
-        <v>-6.5351667073853754</v>
+        <v>-6.6876378392915861</v>
       </c>
       <c r="C27">
         <v>410.1621514722421</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>17.928989061646163</v>
+        <v>17.856977564663275</v>
       </c>
       <c r="B28">
-        <v>-7.7120545354156071</v>
+        <v>-7.8708629298407837</v>
       </c>
       <c r="C28">
         <v>410.1621514722421</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>19.755424544042583</v>
+        <v>19.679100224037722</v>
       </c>
       <c r="B29">
-        <v>-8.9084773746600767</v>
+        <v>-9.0724176994986845</v>
       </c>
       <c r="C29">
         <v>410.1621514722421</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>21.571181055210339</v>
+        <v>21.4910192059884</v>
       </c>
       <c r="B30">
-        <v>-10.124651192959576</v>
+        <v>-10.29251405509028</v>
       </c>
       <c r="C30">
         <v>410.1621514722421</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>23.376664178735787</v>
+        <v>23.293148124618874</v>
       </c>
       <c r="B31">
-        <v>-11.359825855048488</v>
+        <v>-11.530400398821344</v>
       </c>
       <c r="C31">
         <v>410.1621514722421</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>25.172410086507366</v>
+        <v>25.086033151333467</v>
       </c>
       <c r="B32">
-        <v>-12.613009699884621</v>
+        <v>-12.785084256742852</v>
       </c>
       <c r="C32">
         <v>410.1621514722421</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>26.958954950413492</v>
+        <v>26.870220457536462</v>
       </c>
       <c r="B33">
-        <v>-13.883211066425755</v>
+        <v>-14.055573154905753</v>
       </c>
       <c r="C33">
         <v>410.1621514722421</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>28.736622144159767</v>
+        <v>28.646040694797197</v>
       </c>
       <c r="B34">
-        <v>-15.169831868288005</v>
+        <v>-15.3412662506695</v>
       </c>
       <c r="C34">
         <v>410.1621514722421</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>30.50488384872035</v>
+        <v>30.412962435345072</v>
       </c>
       <c r="B35">
-        <v>-16.473848317720716</v>
+        <v>-16.643129226627423</v>
       </c>
       <c r="C35">
         <v>410.1621514722421</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>32.26299944688656</v>
+        <v>32.170238731574486</v>
       </c>
       <c r="B36">
-        <v>-17.796630201631537</v>
+        <v>-17.962519396681326</v>
       </c>
       <c r="C36">
         <v>410.1621514722421</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>34.010228321449752</v>
+        <v>33.917122635879856</v>
       </c>
       <c r="B37">
-        <v>-19.139547306928126</v>
+        <v>-19.30079407473303</v>
       </c>
       <c r="C37">
         <v>410.1621514722421</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>35.74530906880905</v>
+        <v>35.652339460936922</v>
       </c>
       <c r="B38">
-        <v>-20.504932625765569</v>
+        <v>-20.660269555543785</v>
       </c>
       <c r="C38">
         <v>410.1621514722421</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>37.464897139794807</v>
+        <v>37.372503560546477</v>
       </c>
       <c r="B39">
-        <v>-21.898971971288557</v>
+        <v>-22.047098057312539</v>
       </c>
       <c r="C39">
         <v>410.1621514722421</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>39.16512719884517</v>
+        <v>39.073701548790687</v>
       </c>
       <c r="B40">
-        <v>-23.328814361889222</v>
+        <v>-23.468390779097689</v>
       </c>
       <c r="C40">
         <v>410.1621514722421</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>40.84213391039831</v>
+        <v>40.752020039751642</v>
       </c>
       <c r="B41">
-        <v>-24.801608815959678</v>
+        <v>-24.931258919957617</v>
       </c>
       <c r="C41">
         <v>410.1621514722421</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>40.84213391039831</v>
+        <v>40.752020039751642</v>
       </c>
       <c r="B42">
-        <v>-24.801608815959678</v>
+        <v>-24.931258919957617</v>
       </c>
       <c r="C42">
         <v>410.1621514722421</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>38.983467355194186</v>
+        <v>38.889552560004859</v>
       </c>
       <c r="B43">
-        <v>-23.664798015208007</v>
+        <v>-23.803016635871927</v>
       </c>
       <c r="C43">
         <v>410.1621514722421</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>37.132776093933366</v>
+        <v>37.035831715406182</v>
       </c>
       <c r="B44">
-        <v>-22.513236742687162</v>
+        <v>-22.658880426440074</v>
       </c>
       <c r="C44">
         <v>410.1621514722421</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>35.286236884801149</v>
+        <v>35.186976963833942</v>
       </c>
       <c r="B45">
-        <v>-21.353996163529839</v>
+        <v>-21.505901808701534</v>
       </c>
       <c r="C45">
         <v>410.1621514722421</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>33.440026485982763</v>
+        <v>33.3391077631664</v>
       </c>
       <c r="B46">
-        <v>-20.194147442868704</v>
+        <v>-20.351132299695767</v>
       </c>
       <c r="C46">
         <v>410.1621514722421</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>31.590840920564663</v>
+        <v>31.488870133879548</v>
       </c>
       <c r="B47">
-        <v>-19.039801354618369</v>
+        <v>-19.200666574605293</v>
       </c>
       <c r="C47">
         <v>410.1621514722421</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>29.737453271237772</v>
+        <v>29.635016346839912</v>
       </c>
       <c r="B48">
-        <v>-17.893227107820987</v>
+        <v>-18.056771941184842</v>
       </c>
       <c r="C48">
         <v>410.1621514722421</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>27.879155885594177</v>
+        <v>27.776825235511698</v>
       </c>
       <c r="B49">
-        <v>-16.755733520300641</v>
+        <v>-16.920758865332189</v>
       </c>
       <c r="C49">
         <v>410.1621514722421</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>26.015241111225972</v>
+        <v>25.913575633359141</v>
       </c>
       <c r="B50">
-        <v>-15.628629409881418</v>
+        <v>-15.793937812945115</v>
       </c>
       <c r="C50">
         <v>410.1621514722421</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>24.145212444429095</v>
+        <v>24.04476060991632</v>
       </c>
       <c r="B51">
-        <v>-14.51283307047478</v>
+        <v>-14.677229951403383</v>
       </c>
       <c r="C51">
         <v>410.1621514722421</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>22.269417976314834</v>
+        <v>22.170730178996781</v>
       </c>
       <c r="B52">
-        <v>-13.407700700341641</v>
+        <v>-13.569999254014579</v>
       </c>
       <c r="C52">
         <v>410.1621514722421</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>20.388416946698335</v>
+        <v>20.292048590483972</v>
       </c>
       <c r="B53">
-        <v>-12.312197973830324</v>
+        <v>-12.471220395568295</v>
       </c>
       <c r="C53">
         <v>410.1621514722421</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>18.502768595394723</v>
+        <v>18.409280094261298</v>
       </c>
       <c r="B54">
-        <v>-11.225290565289123</v>
+        <v>-11.379868050854091</v>
       </c>
       <c r="C54">
         <v>410.1621514722421</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>16.6129000214132</v>
+        <v>16.522855168430002</v>
       </c>
       <c r="B55">
-        <v>-10.146188546231057</v>
+        <v>-10.29515997770819</v>
       </c>
       <c r="C55">
         <v>410.1621514722421</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>14.718709760539232</v>
+        <v>14.632669203962484</v>
       </c>
       <c r="B56">
-        <v>-9.0750795768279975</v>
+        <v>-9.2172862661534136</v>
       </c>
       <c r="C56">
         <v>410.1621514722421</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>12.819964207752353</v>
+        <v>12.738483820048986</v>
       </c>
       <c r="B57">
-        <v>-8.0123957144165274</v>
+        <v>-8.1466800892592364</v>
       </c>
       <c r="C57">
         <v>410.1621514722421</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>10.916429758032091</v>
+        <v>10.840060635879715</v>
       </c>
       <c r="B58">
-        <v>-6.9585690163332341</v>
+        <v>-7.0837746200951281</v>
       </c>
       <c r="C58">
         <v>410.1621514722421</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>9.0079009679043835</v>
+        <v>8.9371899924118061</v>
       </c>
       <c r="B59">
-        <v>-5.9139794545497661</v>
+        <v>-6.02895084004637</v>
       </c>
       <c r="C59">
         <v>410.1621514722421</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>7.094285040080857</v>
+        <v>7.029777117670104</v>
       </c>
       <c r="B60">
-        <v>-4.878798659578079</v>
+        <v>-4.98238096376152</v>
       </c>
       <c r="C60">
         <v>410.1621514722421</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5.1755173388195495</v>
+        <v>5.1177559614463712</v>
       </c>
       <c r="B61">
-        <v>-3.8531461765651924</v>
+        <v>-3.9441850142049466</v>
       </c>
       <c r="C61">
         <v>410.1621514722421</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3.2515332283785168</v>
+        <v>3.2010604735323871</v>
       </c>
       <c r="B62">
-        <v>-2.8371415506581386</v>
+        <v>-2.91448301434103</v>
       </c>
       <c r="C62">
         <v>410.1621514722421</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.3224433532785651</v>
+        <v>1.2798024654689317</v>
       </c>
       <c r="B63">
-        <v>-1.8305801425179411</v>
+        <v>-1.8930717861187756</v>
       </c>
       <c r="C63">
         <v>410.1621514722421</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.61094052090840634</v>
+        <v>-0.64519480420712427</v>
       </c>
       <c r="B64">
-        <v>-0.83196057486163322</v>
+        <v>-0.87845534742574649</v>
       </c>
       <c r="C64">
         <v>410.1621514722421</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.5476313483477226</v>
+        <v>-2.5729302152098823</v>
       </c>
       <c r="B65">
-        <v>0.1605427140797458</v>
+        <v>0.13118548486585388</v>
       </c>
       <c r="C65">
         <v>410.1621514722421</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.4866420832047318</v>
+        <v>-4.5024026472534695</v>
       </c>
       <c r="B66">
-        <v>1.1487552860751702</v>
+        <v>1.1376698938838357</v>
       </c>
       <c r="C66">
         <v>410.1621514722421</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-6.4282643111474584</v>
+        <v>-6.43390698640416</v>
       </c>
       <c r="B67">
-        <v>2.1321378473762986</v>
+        <v>2.1404620281785847</v>
       </c>
       <c r="C67">
         <v>410.1621514722421</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-8.3779041438547868</v>
+        <v>-8.3729221441369859</v>
       </c>
       <c r="B68">
-        <v>3.100691682165619</v>
+        <v>3.1296058979908876</v>
       </c>
       <c r="C68">
         <v>410.1621514722421</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-10.339750734267005</v>
+        <v>-10.32369318743609</v>
       </c>
       <c r="B69">
-        <v>4.046668865084956</v>
+        <v>4.09738759087411</v>
       </c>
       <c r="C69">
         <v>410.1621514722421</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-12.308010874359139</v>
+        <v>-12.280345779913299</v>
       </c>
       <c r="B70">
-        <v>4.9807840546826352</v>
+        <v>5.0544816419415355</v>
       </c>
       <c r="C70">
         <v>410.1621514722421</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-14.276368355417572</v>
+        <v>-14.236475256270447</v>
       </c>
       <c r="B71">
-        <v>5.9147192101416888</v>
+        <v>6.0125262721081008</v>
       </c>
       <c r="C71">
         <v>410.1621514722421</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-16.246397326939331</v>
+        <v>-16.193675038941684</v>
       </c>
       <c r="B72">
-        <v>6.845562909277394</v>
+        <v>6.9686259979354039</v>
       </c>
       <c r="C72">
         <v>410.1621514722421</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-18.220722324790373</v>
+        <v>-18.154603142094565</v>
       </c>
       <c r="B73">
-        <v>7.7684610185025358</v>
+        <v>7.9179508158811789</v>
       </c>
       <c r="C73">
         <v>410.1621514722421</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-20.19827907210183</v>
+        <v>-20.118177859098044</v>
       </c>
       <c r="B74">
-        <v>8.68538193998767</v>
+        <v>8.862466346341062</v>
       </c>
       <c r="C74">
         <v>410.1621514722421</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-22.17706126558209</v>
+        <v>-22.082362364145776</v>
       </c>
       <c r="B75">
-        <v>9.6000363733350653</v>
+        <v>9.8058738020398231</v>
       </c>
       <c r="C75">
         <v>410.1621514722421</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-24.154983308983365</v>
+        <v>-24.045039075528862</v>
       </c>
       <c r="B76">
-        <v>10.516281672116064</v>
+        <v>10.752021141080872</v>
       </c>
       <c r="C76">
         <v>410.1621514722421</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-26.130115873778418</v>
+        <v>-26.004248625606763</v>
       </c>
       <c r="B77">
-        <v>11.437686169507707</v>
+        <v>11.704468823284099</v>
       </c>
       <c r="C77">
         <v>410.1621514722421</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-28.101233995278289</v>
+        <v>-27.958745258915059</v>
       </c>
       <c r="B78">
-        <v>12.366515463140768</v>
+        <v>12.665480569956728</v>
       </c>
       <c r="C78">
         <v>410.1621514722421</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-30.066239993442398</v>
+        <v>-29.906398362382166</v>
       </c>
       <c r="B79">
-        <v>13.306649255812316</v>
+        <v>13.638928019109004</v>
       </c>
       <c r="C79">
         <v>410.1621514722421</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-32.021443658127616</v>
+        <v>-31.843462600709444</v>
       </c>
       <c r="B80">
-        <v>14.264912667815777</v>
+        <v>14.631616997052957</v>
       </c>
       <c r="C80">
         <v>410.1621514722421</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-33.957759766836752</v>
+        <v>-33.760723411454272</v>
       </c>
       <c r="B81">
-        <v>15.258109006830326</v>
+        <v>15.660291722002832</v>
       </c>
       <c r="C81">
         <v>410.1621514722421</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-35.7113022060782</v>
+        <v>-35.492043909343245</v>
       </c>
       <c r="B82">
-        <v>16.589349043142207</v>
+        <v>17.026847403609086</v>
       </c>
       <c r="C82">
         <v>410.1621514722421</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-41.629686531133935</v>
+        <v>-41.549414414819516</v>
       </c>
       <c r="B1">
-        <v>14.188784061186901</v>
+        <v>14.413494095832078</v>
       </c>
       <c r="C1">
         <v>471.28397822006644</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-39.102712143939875</v>
+        <v>-39.027567560665091</v>
       </c>
       <c r="B2">
-        <v>13.9979881109678</v>
+        <v>14.202769706767969</v>
       </c>
       <c r="C2">
         <v>471.28397822006644</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-36.696466160664222</v>
+        <v>-36.627234301877742</v>
       </c>
       <c r="B3">
-        <v>13.484625372429633</v>
+        <v>13.670481528791211</v>
       </c>
       <c r="C3">
         <v>471.28397822006644</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-34.309608152093496</v>
+        <v>-34.24621900524857</v>
       </c>
       <c r="B4">
-        <v>12.91946109813351</v>
+        <v>13.08707185213038</v>
       </c>
       <c r="C4">
         <v>471.28397822006644</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-31.9365062580502</v>
+        <v>-31.87884267757342</v>
       </c>
       <c r="B5">
-        <v>12.317542708493804</v>
+        <v>12.467569106867073</v>
       </c>
       <c r="C5">
         <v>471.28397822006644</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-29.574865005509096</v>
+        <v>-29.522790859740962</v>
       </c>
       <c r="B6">
-        <v>11.685003336538001</v>
+        <v>11.818098091126755</v>
       </c>
       <c r="C6">
         <v>471.28397822006644</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-27.223374617375022</v>
+        <v>-27.17674308109445</v>
       </c>
       <c r="B7">
-        <v>11.025342495034304</v>
+        <v>11.142153192070362</v>
       </c>
       <c r="C7">
         <v>471.28397822006644</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-24.881265430909039</v>
+        <v>-24.839923530581768</v>
       </c>
       <c r="B8">
-        <v>10.340616598461244</v>
+        <v>10.441787453562231</v>
       </c>
       <c r="C8">
         <v>471.28397822006644</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-22.547333504114508</v>
+        <v>-22.511118417792421</v>
       </c>
       <c r="B9">
-        <v>9.6340423853043529</v>
+        <v>9.7202129527543946</v>
       </c>
       <c r="C9">
         <v>471.28397822006644</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-20.220278865785879</v>
+        <v>-20.189017095981683</v>
       </c>
       <c r="B10">
-        <v>8.9090931685792274</v>
+        <v>8.98089807959855</v>
       </c>
       <c r="C10">
         <v>471.28397822006644</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-17.898851707139666</v>
+        <v>-17.872359472426123</v>
       </c>
       <c r="B11">
-        <v>8.1691082354147753</v>
+        <v>8.2271774419572967</v>
       </c>
       <c r="C11">
         <v>471.28397822006644</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-15.582385201166535</v>
+        <v>-15.560473342643839</v>
       </c>
       <c r="B12">
-        <v>7.4158692398359376</v>
+        <v>7.460829907614694</v>
       </c>
       <c r="C12">
         <v>471.28397822006644</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-13.272494285531643</v>
+        <v>-13.254987501097705</v>
       </c>
       <c r="B13">
-        <v>6.6450613293384508</v>
+        <v>6.6775451661297058</v>
       </c>
       <c r="C13">
         <v>471.28397822006644</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-10.970145057573344</v>
+        <v>-10.956876407252734</v>
       </c>
       <c r="B14">
-        <v>5.8541032479334705</v>
+        <v>5.8747444864824327</v>
       </c>
       <c r="C14">
         <v>471.28397822006644</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-8.6714264886483381</v>
+        <v>-8.6621961816377731</v>
       </c>
       <c r="B15">
-        <v>5.0534446322230648</v>
+        <v>5.062864633562663</v>
       </c>
       <c r="C15">
         <v>471.28397822006644</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-6.3727514020687</v>
+        <v>-6.3673295168402024</v>
       </c>
       <c r="B16">
-        <v>4.2526698387116042</v>
+        <v>4.2514781582751064</v>
       </c>
       <c r="C16">
         <v>471.28397822006644</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-4.0767051549496545</v>
+        <v>-4.0748837326176552</v>
       </c>
       <c r="B17">
-        <v>3.4448712109217778</v>
+        <v>3.4336852596744794</v>
       </c>
       <c r="C17">
         <v>471.28397822006644</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.7866261605495402</v>
+        <v>-1.7882255443063913</v>
       </c>
       <c r="B18">
-        <v>2.6211290480386498</v>
+        <v>2.6005765335378217</v>
       </c>
       <c r="C18">
         <v>471.28397822006644</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.49730747710419176</v>
+        <v>0.49246537761328274</v>
       </c>
       <c r="B19">
-        <v>1.7809674848784092</v>
+        <v>1.7516765143813855</v>
       </c>
       <c r="C19">
         <v>471.28397822006644</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.7757077312918259</v>
+        <v>2.7678061238750629</v>
       </c>
       <c r="B20">
-        <v>0.926021615165022</v>
+        <v>0.88861822140621827</v>
       </c>
       <c r="C20">
         <v>471.28397822006644</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>5.0491865752936018</v>
+        <v>5.0384137852125992</v>
       </c>
       <c r="B21">
-        <v>0.0579265326224709</v>
+        <v>0.013034673813386473</v>
       </c>
       <c r="C21">
         <v>471.28397822006644</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>7.3182470507673854</v>
+        <v>7.3047956172248885</v>
       </c>
       <c r="B22">
-        <v>-0.82197371671951813</v>
+        <v>-0.87373176804754549</v>
       </c>
       <c r="C22">
         <v>471.28397822006644</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>9.5829564728813565</v>
+        <v>9.56701953497212</v>
       </c>
       <c r="B23">
-        <v>-1.7134992776081675</v>
+        <v>-1.7715013792329444</v>
       </c>
       <c r="C23">
         <v>471.28397822006644</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>11.843273225181259</v>
+        <v>11.82504361837977</v>
       </c>
       <c r="B24">
-        <v>-2.6167613424849332</v>
+        <v>-2.6803850936506555</v>
       </c>
       <c r="C24">
         <v>471.28397822006644</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>14.099155691212861</v>
+        <v>14.078825947373332</v>
       </c>
       <c r="B25">
-        <v>-3.5318711037912798</v>
+        <v>-3.600493845208534</v>
       </c>
       <c r="C25">
         <v>471.28397822006644</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>16.350544299954159</v>
+        <v>16.328306511346767</v>
       </c>
       <c r="B26">
-        <v>-4.4589877256726655</v>
+        <v>-4.5319864411395612</v>
       </c>
       <c r="C26">
         <v>471.28397822006644</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>18.597307662112147</v>
+        <v>18.573352937567986</v>
       </c>
       <c r="B27">
-        <v>-5.3984622590905573</v>
+        <v>-5.4752131819772787</v>
       </c>
       <c r="C27">
         <v>471.28397822006644</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>20.839296433826011</v>
+        <v>20.813814762773315</v>
       </c>
       <c r="B28">
-        <v>-6.3506937267104062</v>
+        <v>-6.4305722415803368</v>
       </c>
       <c r="C28">
         <v>471.28397822006644</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>23.076361271235</v>
+        <v>23.049541523699151</v>
       </c>
       <c r="B29">
-        <v>-7.3160811511976771</v>
+        <v>-7.3984617938074173</v>
       </c>
       <c r="C29">
         <v>471.28397822006644</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>25.308433974574811</v>
+        <v>25.280464602084539</v>
       </c>
       <c r="B30">
-        <v>-8.2948067513029748</v>
+        <v>-8.3790634244959</v>
       </c>
       <c r="C30">
         <v>471.28397822006644</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>27.53577092046724</v>
+        <v>27.506842759679458</v>
       </c>
       <c r="B31">
-        <v>-9.2861855301175158</v>
+        <v>-9.371692367398099</v>
       </c>
       <c r="C31">
         <v>471.28397822006644</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>29.758709629630577</v>
+        <v>29.729016603236605</v>
       </c>
       <c r="B32">
-        <v>-10.28931568681768</v>
+        <v>-10.375447268245058</v>
       </c>
       <c r="C32">
         <v>471.28397822006644</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>31.977587622783105</v>
+        <v>31.947326739508647</v>
       </c>
       <c r="B33">
-        <v>-11.303295420579831</v>
+        <v>-11.389426772767802</v>
       </c>
       <c r="C33">
         <v>471.28397822006644</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>34.192611288895954</v>
+        <v>34.161981552743207</v>
       </c>
       <c r="B34">
-        <v>-12.327573293420798</v>
+        <v>-12.413079429682064</v>
       </c>
       <c r="C34">
         <v>471.28397822006644</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>36.403462489951728</v>
+        <v>36.372660537167796</v>
       </c>
       <c r="B35">
-        <v>-13.362999318719318</v>
+        <v>-13.44725339964236</v>
       </c>
       <c r="C35">
         <v>471.28397822006644</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>38.609691956185841</v>
+        <v>38.578910964504843</v>
       </c>
       <c r="B36">
-        <v>-14.410773872694564</v>
+        <v>-14.493146746287879</v>
       </c>
       <c r="C36">
         <v>471.28397822006644</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>40.810850417833727</v>
+        <v>40.7802801064768</v>
       </c>
       <c r="B37">
-        <v>-15.472097331565736</v>
+        <v>-15.551957533257831</v>
       </c>
       <c r="C37">
         <v>471.28397822006644</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>43.006167024074657</v>
+        <v>42.975990953336108</v>
       </c>
       <c r="B38">
-        <v>-16.549029284174043</v>
+        <v>-16.625741976547626</v>
       </c>
       <c r="C38">
         <v>471.28397822006644</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>45.193584599863051</v>
+        <v>45.163969369455074</v>
       </c>
       <c r="B39">
-        <v>-17.647066169848713</v>
+        <v>-17.719988901577484</v>
       </c>
       <c r="C39">
         <v>471.28397822006644</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>47.370724389097155</v>
+        <v>47.341816937735985</v>
       </c>
       <c r="B40">
-        <v>-18.772563640541009</v>
+        <v>-18.841045286123826</v>
       </c>
       <c r="C40">
         <v>471.28397822006644</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>49.535207635675221</v>
+        <v>49.507135241081173</v>
       </c>
       <c r="B41">
-        <v>-19.931877348202189</v>
+        <v>-19.995258107963089</v>
       </c>
       <c r="C41">
         <v>471.28397822006644</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>49.535207635675221</v>
+        <v>49.507135241081173</v>
       </c>
       <c r="B42">
-        <v>-19.931877348202189</v>
+        <v>-19.995258107963089</v>
       </c>
       <c r="C42">
         <v>471.28397822006644</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>47.258410836738733</v>
+        <v>47.22855508897343</v>
       </c>
       <c r="B43">
-        <v>-19.072647305139498</v>
+        <v>-19.140772317632685</v>
       </c>
       <c r="C43">
         <v>471.28397822006644</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>44.988246459501347</v>
+        <v>44.956897498692641</v>
       </c>
       <c r="B44">
-        <v>-18.195696502944571</v>
+        <v>-18.267967217406692</v>
       </c>
       <c r="C44">
         <v>471.28397822006644</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>42.722339697470076</v>
+        <v>42.689767189012606</v>
       </c>
       <c r="B45">
-        <v>-17.307370040852202</v>
+        <v>-17.383181486543773</v>
       </c>
       <c r="C45">
         <v>471.28397822006644</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>40.458315744151925</v>
+        <v>40.424768878707191</v>
       </c>
       <c r="B46">
-        <v>-16.414013018097208</v>
+        <v>-16.492753804302595</v>
       </c>
       <c r="C46">
         <v>471.28397822006644</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>38.194121237187233</v>
+        <v>38.159831459520774</v>
       </c>
       <c r="B47">
-        <v>-15.521111687128231</v>
+        <v>-15.602164984709887</v>
       </c>
       <c r="C47">
         <v>471.28397822006644</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>35.928988590749547</v>
+        <v>35.894180515079952</v>
       </c>
       <c r="B48">
-        <v>-14.630716913249225</v>
+        <v>-14.713464380864538</v>
       </c>
       <c r="C48">
         <v>471.28397822006644</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>33.662471663145688</v>
+        <v>33.627365801981881</v>
       </c>
       <c r="B49">
-        <v>-13.744020714977969</v>
+        <v>-13.82784348063349</v>
       </c>
       <c r="C49">
         <v>471.28397822006644</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>31.39412431268255</v>
+        <v>31.358937076823747</v>
       </c>
       <c r="B50">
-        <v>-12.862215110832267</v>
+        <v>-12.946493771883704</v>
       </c>
       <c r="C50">
         <v>471.28397822006644</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>29.123631376576181</v>
+        <v>29.088576197431497</v>
       </c>
       <c r="B51">
-        <v>-11.986142164847633</v>
+        <v>-12.070257160433071</v>
       </c>
       <c r="C51">
         <v>471.28397822006644</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>26.851201607679588</v>
+        <v>26.816493426546344</v>
       </c>
       <c r="B52">
-        <v>-11.11524412313055</v>
+        <v>-11.198577223903302</v>
       </c>
       <c r="C52">
         <v>471.28397822006644</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>24.577174737755019</v>
+        <v>24.543031128138317</v>
       </c>
       <c r="B53">
-        <v>-10.248613277305239</v>
+        <v>-10.330547957867074</v>
       </c>
       <c r="C53">
         <v>471.28397822006644</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>22.301890498564688</v>
+        <v>22.268531666177406</v>
       </c>
       <c r="B54">
-        <v>-9.38534191899591</v>
+        <v>-9.46526335789705</v>
       </c>
       <c r="C54">
         <v>471.28397822006644</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>20.025607330291734</v>
+        <v>19.993255442468502</v>
       </c>
       <c r="B55">
-        <v>-8.5247395377911861</v>
+        <v>-8.6020343176362832</v>
       </c>
       <c r="C55">
         <v>471.28397822006644</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>17.748258506803079</v>
+        <v>17.717135010156056</v>
       </c>
       <c r="B56">
-        <v>-7.6669844151373523</v>
+        <v>-7.7410393230094305</v>
       </c>
       <c r="C56">
         <v>471.28397822006644</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>15.469696010386492</v>
+        <v>15.440020960219368</v>
       </c>
       <c r="B57">
-        <v>-6.8124720304450834</v>
+        <v>-6.8826737580115189</v>
       </c>
       <c r="C57">
         <v>471.28397822006644</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>13.189771823329824</v>
+        <v>13.161763883637784</v>
       </c>
       <c r="B58">
-        <v>-5.9615978631250766</v>
+        <v>-6.0273330066375985</v>
       </c>
       <c r="C58">
         <v>471.28397822006644</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>10.908355736078272</v>
+        <v>10.882232345539469</v>
       </c>
       <c r="B59">
-        <v>-5.1147098120687984</v>
+        <v>-5.1753648875432363</v>
       </c>
       <c r="C59">
         <v>471.28397822006644</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>8.6253887717067172</v>
+        <v>8.6013668076481036</v>
       </c>
       <c r="B60">
-        <v>-4.27196545409087</v>
+        <v>-4.3269269580261494</v>
       </c>
       <c r="C60">
         <v>471.28397822006644</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>6.340829761447436</v>
+        <v>6.3191257058362211</v>
       </c>
       <c r="B61">
-        <v>-3.4334747854866943</v>
+        <v>-3.482129210044588</v>
       </c>
       <c r="C61">
         <v>471.28397822006644</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4.054637536532729</v>
+        <v>4.0354674759763771</v>
       </c>
       <c r="B62">
-        <v>-2.5993478025516823</v>
+        <v>-2.6410816355568065</v>
       </c>
       <c r="C62">
         <v>471.28397822006644</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.766879707691803</v>
+        <v>1.7504602681248676</v>
       </c>
       <c r="B63">
-        <v>-1.7694038603417255</v>
+        <v>-1.8036038877444005</v>
       </c>
       <c r="C63">
         <v>471.28397822006644</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.52194099635842928</v>
+        <v>-0.53538891092700935</v>
       </c>
       <c r="B64">
-        <v>-0.94229974895465551</v>
+        <v>-0.96835426468233776</v>
       </c>
       <c r="C64">
         <v>471.28397822006644</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.8112130674040854</v>
+        <v>-2.8214633402041533</v>
       </c>
       <c r="B65">
-        <v>-0.11640161724880678</v>
+        <v>-0.13370072566894731</v>
       </c>
       <c r="C65">
         <v>471.28397822006644</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-5.1003249972313274</v>
+        <v>-5.1071462987315108</v>
       </c>
       <c r="B66">
-        <v>0.70992438591750351</v>
+        <v>0.70198876999745874</v>
       </c>
       <c r="C66">
         <v>471.28397822006644</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-7.3894554771980081</v>
+        <v>-7.3926179239426091</v>
       </c>
       <c r="B67">
-        <v>1.5362008261085303</v>
+        <v>1.5382375211257455</v>
       </c>
       <c r="C67">
         <v>471.28397822006644</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-9.6819439969488048</v>
+        <v>-9.68124578690537</v>
       </c>
       <c r="B68">
-        <v>2.3535051265788445</v>
+        <v>2.3661338589535075</v>
       </c>
       <c r="C68">
         <v>471.28397822006644</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-11.980377166381091</v>
+        <v>-11.975638203315631</v>
       </c>
       <c r="B69">
-        <v>3.154926283619766</v>
+        <v>3.1787753469649576</v>
       </c>
       <c r="C69">
         <v>471.28397822006644</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-14.281169278116002</v>
+        <v>-14.272179033746298</v>
       </c>
       <c r="B70">
-        <v>3.9500447279792374</v>
+        <v>3.9857314452019694</v>
       </c>
       <c r="C70">
         <v>471.28397822006644</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-16.580410906256446</v>
+        <v>-16.566925672726953</v>
       </c>
       <c r="B71">
-        <v>4.749305813980417</v>
+        <v>4.7974355471414247</v>
       </c>
       <c r="C71">
         <v>471.28397822006644</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-18.879070068108593</v>
+        <v>-18.860854105736749</v>
       </c>
       <c r="B72">
-        <v>5.5501231557906827</v>
+        <v>5.61130488344258</v>
       </c>
       <c r="C72">
         <v>471.28397822006644</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-21.178763773681297</v>
+        <v>-21.155594774272981</v>
       </c>
       <c r="B73">
-        <v>6.3481763639382489</v>
+        <v>6.4230247850851461</v>
       </c>
       <c r="C73">
         <v>471.28397822006644</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-23.47882756059083</v>
+        <v>-23.450477352956028</v>
       </c>
       <c r="B74">
-        <v>7.1452407745504622</v>
+        <v>7.234369147148306</v>
       </c>
       <c r="C74">
         <v>471.28397822006644</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-25.778014132062903</v>
+        <v>-25.744243745153796</v>
       </c>
       <c r="B75">
-        <v>7.9446489630736314</v>
+        <v>8.0486672951994187</v>
       </c>
       <c r="C75">
         <v>471.28397822006644</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-28.075026326153374</v>
+        <v>-28.035585536101181</v>
       </c>
       <c r="B76">
-        <v>8.7498667366307465</v>
+        <v>8.86938171265908</v>
       </c>
       <c r="C76">
         <v>471.28397822006644</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-30.368663161827609</v>
+        <v>-30.323291287703864</v>
       </c>
       <c r="B77">
-        <v>9.5641029224952625</v>
+        <v>9.6997182516993341</v>
       </c>
       <c r="C77">
         <v>471.28397822006644</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-32.658158246858783</v>
+        <v>-32.606587786683683</v>
       </c>
       <c r="B78">
-        <v>10.389405196865791</v>
+        <v>10.541723081644772</v>
       </c>
       <c r="C78">
         <v>471.28397822006644</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-34.94220521462357</v>
+        <v>-34.884157271106936</v>
       </c>
       <c r="B79">
-        <v>11.229263960280868</v>
+        <v>11.398883421509984</v>
       </c>
       <c r="C79">
         <v>471.28397822006644</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-37.218512280227877</v>
+        <v>-37.15368821059581</v>
       </c>
       <c r="B80">
-        <v>12.089802491677453</v>
+        <v>12.277316319055931</v>
       </c>
       <c r="C80">
         <v>471.28397822006644</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-39.481451485584095</v>
+        <v>-39.409504710127216</v>
       </c>
       <c r="B81">
-        <v>12.986057785716218</v>
+        <v>13.192042005587473</v>
       </c>
       <c r="C81">
         <v>471.28397822006644</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-41.629686531133935</v>
+        <v>-41.549414414819516</v>
       </c>
       <c r="B82">
-        <v>14.188784061186901</v>
+        <v>14.413494095832078</v>
       </c>
       <c r="C82">
         <v>471.28397822006644</v>
